--- a/dataset/ckg_data.xlsx
+++ b/dataset/ckg_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12800"/>
+    <workbookView windowHeight="16420" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="persiapan" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="599">
   <si>
     <t>nik</t>
   </si>
@@ -95,12 +95,18 @@
     <t>desa</t>
   </si>
   <si>
+    <t>351xxx</t>
+  </si>
+  <si>
+    <t>NURUL ZAMZAMAH</t>
+  </si>
+  <si>
+    <t>1985-04-24</t>
+  </si>
+  <si>
     <t>Perempuan</t>
   </si>
   <si>
-    <t>isikan nomor whatsapp wali</t>
-  </si>
-  <si>
     <t>Menikah</t>
   </si>
   <si>
@@ -125,12 +131,6 @@
     <t> </t>
   </si>
   <si>
-    <t>MUHAMMAD HAEDAR ALI</t>
-  </si>
-  <si>
-    <t>2026-10-07</t>
-  </si>
-  <si>
     <t>batas_awal</t>
   </si>
   <si>
@@ -485,6 +485,9 @@
     <t>ABDUL xxx</t>
   </si>
   <si>
+    <t>SUCCESS</t>
+  </si>
+  <si>
     <t>Ya</t>
   </si>
   <si>
@@ -833,12 +836,15 @@
     <t>hepatitis_c</t>
   </si>
   <si>
+    <t>2026-10-02</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
     <t>ATIYATUN NAWARO</t>
   </si>
   <si>
-    <t>SUCCESS</t>
-  </si>
-  <si>
     <t>Normal (visus 6/6 - 6/9)</t>
   </si>
   <si>
@@ -1823,7 +1829,7 @@
     <t>Kelas 2</t>
   </si>
   <si>
-    <t>Putri S</t>
+    <t>Putri Shidqiyah</t>
   </si>
   <si>
     <t>Bayi Kuning Kramer 1-3</t>
@@ -2453,6 +2459,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2717,7 +2724,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{9FE5D190-0E83-E65B-0162-C66A1C2E7DF5}">
+    <tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="7" xr9:uid="{17107907-8548-717A-D0DF-C66A1A871967}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -2726,7 +2733,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{1D5EA0AC-2E16-4897-0162-C66AE2B53BBE}">
+    <tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="10" xr9:uid="{C0460F1B-D309-7DD4-D0DF-C66A73AAB901}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -2934,18 +2941,18 @@
   <dimension ref="A1:R92"/>
   <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="5.3515625" customWidth="1"/>
+    <col min="1" max="1" width="18.3125" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="3" max="3" width="5.640625" customWidth="1"/>
-    <col min="4" max="4" width="5.3515625" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="5.4921875" customWidth="1"/>
     <col min="6" max="6" width="5.640625" customWidth="1"/>
     <col min="7" max="7" width="16.921875" customWidth="1"/>
     <col min="8" max="8" width="7.234375" customWidth="1"/>
     <col min="9" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="10" width="6.0703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.0625" style="1" customWidth="1"/>
     <col min="11" max="11" width="7.0859375" customWidth="1"/>
-    <col min="12" max="12" width="24.6875" customWidth="1"/>
+    <col min="12" max="12" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:18">
@@ -3029,36 +3036,151 @@
         <f>[1]Sheet1!$J14</f>
         <v>0</v>
       </c>
+      <c r="H2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2"/>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="5">
+        <f>[1]Sheet1!$E15</f>
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <f>[1]Sheet1!$C15</f>
+        <v>0</v>
+      </c>
+      <c r="D3" t="str">
+        <f>RIGHT([1]Sheet1!$N15,10)</f>
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <f>IF([1]Sheet1!$I15="L","Laki-laki","Perempuan")</f>
+        <v>Perempuan</v>
+      </c>
+      <c r="F3" t="str">
+        <f>IF(LEFT([1]Sheet1!$H15,2)="08",MID([1]Sheet1!$H15,2,11),"8123456789")</f>
+        <v>8123456789</v>
+      </c>
+      <c r="G3">
+        <f>[1]Sheet1!$J15</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L2" t="s">
+      <c r="I3" t="s">
         <v>19</v>
       </c>
-      <c r="M2" t="s">
+      <c r="J3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N2" t="s">
+      <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="O2" t="s">
+      <c r="L3"/>
+      <c r="M3" t="s">
         <v>22</v>
       </c>
-      <c r="P2" t="s">
+      <c r="N3" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="O3" t="s">
         <v>24</v>
       </c>
-      <c r="R2" t="s">
+      <c r="P3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="5"/>
+      <c r="Q3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="5"/>
+      <c r="A4" s="5">
+        <f>[1]Sheet1!$E16</f>
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <f>[1]Sheet1!$C16</f>
+        <v>0</v>
+      </c>
+      <c r="D4" t="str">
+        <f>RIGHT([1]Sheet1!$N16,10)</f>
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <f>IF([1]Sheet1!$I16="L","Laki-laki","Perempuan")</f>
+        <v>Perempuan</v>
+      </c>
+      <c r="F4" t="str">
+        <f>IF(LEFT([1]Sheet1!$H16,2)="08",MID([1]Sheet1!$H16,2,11),"8123456789")</f>
+        <v>8123456789</v>
+      </c>
+      <c r="G4">
+        <f>[1]Sheet1!$J16</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4"/>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="5"/>
@@ -3345,10 +3467,10 @@
         <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E1" t="s">
         <v>33</v>
@@ -3630,7 +3752,7 @@
         <v>132</v>
       </c>
       <c r="CT1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="CU1" t="s">
         <v>134</v>
@@ -3656,112 +3778,112 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:105">
       <c r="A2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="T2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="U2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="V2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="W2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="X2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AA2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AB2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AC2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AD2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AH2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AI2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AJ2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AK2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AL2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AM2">
         <v>5</v>
@@ -3770,61 +3892,61 @@
         <v>100</v>
       </c>
       <c r="AO2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AP2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AQ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AR2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AS2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AT2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AU2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AV2">
         <v>10</v>
       </c>
       <c r="AW2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AX2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AY2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AZ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BA2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BB2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BD2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BF2" t="s">
         <v>152</v>
       </c>
-      <c r="BE2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>151</v>
-      </c>
       <c r="BG2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BH2">
         <v>2900</v>
@@ -3833,7 +3955,7 @@
         <v>6000</v>
       </c>
       <c r="BJ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BK2">
         <v>80</v>
@@ -3842,127 +3964,127 @@
         <v>90</v>
       </c>
       <c r="BM2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BN2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BO2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BP2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BQ2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BR2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BS2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BT2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BU2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BV2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BW2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BX2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BY2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BZ2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CA2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CB2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="CC2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CD2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="CE2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="CF2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="CG2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CH2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="CI2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="CJ2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CK2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="CL2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CM2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="CN2" t="s">
+        <v>166</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>275</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>276</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CS2" t="s">
         <v>165</v>
       </c>
-      <c r="CO2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>273</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>274</v>
-      </c>
-      <c r="CR2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CS2" t="s">
-        <v>164</v>
-      </c>
       <c r="CT2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CU2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="CV2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="CW2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="CX2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="CY2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="CZ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="DA2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -3980,13 +4102,13 @@
   <cols>
     <col min="1" max="1" width="4.921875" customWidth="1"/>
     <col min="2" max="2" width="8.6796875" customWidth="1"/>
-    <col min="3" max="3" width="139.75" customWidth="1"/>
-    <col min="4" max="4" width="6.421875" customWidth="1"/>
+    <col min="3" max="3" width="6.3125" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="7.078125" customWidth="1"/>
     <col min="8" max="8" width="5.7890625" customWidth="1"/>
     <col min="9" max="9" width="6.078125" customWidth="1"/>
-    <col min="10" max="10" width="6.5078125" customWidth="1"/>
+    <col min="10" max="10" width="12.0625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:18">
@@ -4054,90 +4176,433 @@
       <c r="M2"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" ht="16.5" customHeight="1"/>
-    <row r="4" ht="16.5" customHeight="1"/>
-    <row r="5" ht="16.5" customHeight="1"/>
-    <row r="6" ht="16.5" customHeight="1"/>
-    <row r="7" ht="16.5" customHeight="1"/>
-    <row r="8" ht="16.5" customHeight="1"/>
-    <row r="9" ht="16.5" customHeight="1"/>
-    <row r="10" ht="16.5" customHeight="1"/>
-    <row r="11" ht="16.5" customHeight="1"/>
-    <row r="12" ht="16.5" customHeight="1"/>
-    <row r="13" ht="16.5" customHeight="1"/>
-    <row r="14" ht="16.5" customHeight="1"/>
-    <row r="15" ht="16.5" customHeight="1"/>
-    <row r="16" ht="16.5" customHeight="1"/>
-    <row r="17" ht="16.5" customHeight="1"/>
-    <row r="18" ht="16.5" customHeight="1"/>
-    <row r="19" ht="16.5" customHeight="1"/>
-    <row r="20" ht="16.5" customHeight="1"/>
-    <row r="21" ht="16.5" customHeight="1"/>
-    <row r="22" ht="16.5" customHeight="1"/>
-    <row r="23" ht="16.5" customHeight="1"/>
-    <row r="24" ht="16.5" customHeight="1"/>
-    <row r="25" ht="16.5" customHeight="1"/>
-    <row r="26" ht="16.5" customHeight="1"/>
-    <row r="27" ht="16.5" customHeight="1"/>
-    <row r="28" ht="16.5" customHeight="1"/>
-    <row r="29" ht="16.5" customHeight="1"/>
-    <row r="30" ht="16.5" customHeight="1"/>
-    <row r="31" ht="16.5" customHeight="1"/>
-    <row r="32" ht="16.5" customHeight="1"/>
-    <row r="33" ht="16.5" customHeight="1"/>
-    <row r="34" ht="16.5" customHeight="1"/>
-    <row r="35" ht="16.5" customHeight="1"/>
-    <row r="36" ht="16.5" customHeight="1"/>
-    <row r="37" ht="16.5" customHeight="1"/>
-    <row r="38" ht="16.5" customHeight="1"/>
-    <row r="39" ht="16.5" customHeight="1"/>
-    <row r="40" ht="16.5" customHeight="1"/>
-    <row r="41" ht="16.5" customHeight="1"/>
-    <row r="42" ht="16.5" customHeight="1"/>
-    <row r="43" ht="16.5" customHeight="1"/>
-    <row r="44" ht="16.5" customHeight="1"/>
-    <row r="45" ht="16.5" customHeight="1"/>
-    <row r="46" ht="16.5" customHeight="1"/>
-    <row r="47" ht="16.5" customHeight="1"/>
-    <row r="48" ht="16.5" customHeight="1"/>
-    <row r="49" ht="16.5" customHeight="1"/>
-    <row r="50" ht="16.5" customHeight="1"/>
-    <row r="51" ht="16.5" customHeight="1"/>
-    <row r="52" ht="16.5" customHeight="1"/>
-    <row r="53" ht="16.5" customHeight="1"/>
-    <row r="54" ht="16.5" customHeight="1"/>
-    <row r="55" ht="16.5" customHeight="1"/>
-    <row r="56" ht="16.5" customHeight="1"/>
-    <row r="57" ht="16.5" customHeight="1"/>
-    <row r="58" ht="16.5" customHeight="1"/>
-    <row r="59" ht="16.5" customHeight="1"/>
-    <row r="60" ht="16.5" customHeight="1"/>
-    <row r="61" ht="16.5" customHeight="1"/>
-    <row r="62" ht="16.5" customHeight="1"/>
-    <row r="63" ht="16.5" customHeight="1"/>
-    <row r="64" ht="16.5" customHeight="1"/>
-    <row r="65" ht="16.5" customHeight="1"/>
-    <row r="66" ht="16.5" customHeight="1"/>
-    <row r="67" ht="16.5" customHeight="1"/>
-    <row r="68" ht="16.5" customHeight="1"/>
-    <row r="69" ht="16.5" customHeight="1"/>
-    <row r="70" ht="16.5" customHeight="1"/>
-    <row r="71" ht="16.5" customHeight="1"/>
-    <row r="72" ht="16.5" customHeight="1"/>
-    <row r="73" ht="16.5" customHeight="1"/>
-    <row r="74" ht="16.5" customHeight="1"/>
-    <row r="75" ht="16.5" customHeight="1"/>
-    <row r="76" ht="16.5" customHeight="1"/>
-    <row r="77" ht="16.5" customHeight="1"/>
-    <row r="78" ht="16.5" customHeight="1"/>
-    <row r="79" ht="16.5" customHeight="1"/>
-    <row r="80" ht="16.5" customHeight="1"/>
-    <row r="81" ht="16.5" customHeight="1"/>
-    <row r="82" ht="16.5" customHeight="1"/>
-    <row r="83" ht="16.5" customHeight="1"/>
-    <row r="84" ht="16.5" customHeight="1"/>
-    <row r="85" ht="16.5" customHeight="1"/>
-    <row r="86" ht="16.5" customHeight="1"/>
+    <row r="3" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J3" s="1"/>
+      <c r="K3"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J4" s="1"/>
+      <c r="K4"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J5" s="1"/>
+      <c r="K5"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J6" s="1"/>
+      <c r="K6"/>
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J7" s="1"/>
+      <c r="K7"/>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J8" s="1"/>
+      <c r="K8"/>
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J9" s="1"/>
+      <c r="K9"/>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J10" s="1"/>
+      <c r="K10"/>
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" spans="1:18">
+      <c r="C11" s="4"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11" s="1"/>
+      <c r="K11"/>
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J12" s="1"/>
+      <c r="K12"/>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J13" s="1"/>
+      <c r="K13"/>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J14" s="1"/>
+      <c r="K14"/>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J15" s="1"/>
+      <c r="K15"/>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" ht="16.5" customHeight="1" spans="1:18">
+      <c r="J16" s="1"/>
+      <c r="K16"/>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J17" s="1"/>
+      <c r="K17"/>
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J18" s="1"/>
+      <c r="K18"/>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J19" s="1"/>
+      <c r="K19"/>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J20" s="1"/>
+      <c r="K20"/>
+      <c r="L20" s="1"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J21" s="1"/>
+      <c r="K21"/>
+      <c r="L21" s="1"/>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J22" s="1"/>
+      <c r="K22"/>
+      <c r="L22" s="1"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J23" s="1"/>
+      <c r="K23"/>
+      <c r="L23" s="1"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J24" s="1"/>
+      <c r="K24"/>
+      <c r="L24" s="1"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J25" s="1"/>
+      <c r="K25"/>
+      <c r="L25" s="1"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J26" s="1"/>
+      <c r="K26"/>
+      <c r="L26" s="1"/>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J27" s="1"/>
+      <c r="K27"/>
+      <c r="L27" s="1"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J28" s="1"/>
+      <c r="K28"/>
+      <c r="L28" s="1"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J29" s="1"/>
+      <c r="K29"/>
+      <c r="L29" s="1"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J30" s="1"/>
+      <c r="K30"/>
+      <c r="L30" s="1"/>
+    </row>
+    <row r="31" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J31" s="1"/>
+      <c r="K31"/>
+      <c r="L31" s="1"/>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J32" s="1"/>
+      <c r="K32"/>
+      <c r="L32" s="1"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J33" s="1"/>
+      <c r="K33"/>
+      <c r="L33" s="1"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J34" s="1"/>
+      <c r="K34"/>
+      <c r="L34" s="1"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J35" s="1"/>
+      <c r="K35"/>
+      <c r="L35" s="1"/>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J36" s="1"/>
+      <c r="K36"/>
+      <c r="L36" s="1"/>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J37" s="1"/>
+      <c r="K37"/>
+      <c r="L37" s="1"/>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J38" s="1"/>
+      <c r="K38"/>
+      <c r="L38" s="1"/>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J39" s="1"/>
+      <c r="K39"/>
+      <c r="L39" s="1"/>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J40" s="1"/>
+      <c r="K40"/>
+      <c r="L40" s="1"/>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J41" s="1"/>
+      <c r="K41"/>
+      <c r="L41" s="1"/>
+    </row>
+    <row r="42" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J42" s="1"/>
+      <c r="K42"/>
+      <c r="L42" s="1"/>
+    </row>
+    <row r="43" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J43" s="1"/>
+      <c r="K43"/>
+      <c r="L43" s="1"/>
+    </row>
+    <row r="44" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J44" s="1"/>
+      <c r="K44"/>
+      <c r="L44" s="1"/>
+    </row>
+    <row r="45" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J45" s="1"/>
+      <c r="K45"/>
+      <c r="L45" s="1"/>
+    </row>
+    <row r="46" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J46" s="1"/>
+      <c r="K46"/>
+      <c r="L46" s="1"/>
+    </row>
+    <row r="47" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J47" s="1"/>
+      <c r="K47"/>
+      <c r="L47" s="1"/>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J48" s="1"/>
+      <c r="K48"/>
+      <c r="L48" s="1"/>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J49" s="1"/>
+      <c r="K49"/>
+      <c r="L49" s="1"/>
+    </row>
+    <row r="50" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J50" s="1"/>
+      <c r="K50"/>
+      <c r="L50" s="1"/>
+    </row>
+    <row r="51" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J51" s="1"/>
+      <c r="K51"/>
+      <c r="L51" s="1"/>
+    </row>
+    <row r="52" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J52" s="1"/>
+      <c r="K52"/>
+      <c r="L52" s="1"/>
+    </row>
+    <row r="53" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J53" s="1"/>
+      <c r="K53"/>
+      <c r="L53" s="1"/>
+    </row>
+    <row r="54" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J54" s="1"/>
+      <c r="K54"/>
+      <c r="L54" s="1"/>
+    </row>
+    <row r="55" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J55" s="1"/>
+      <c r="K55"/>
+      <c r="L55" s="1"/>
+    </row>
+    <row r="56" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J56" s="1"/>
+      <c r="K56"/>
+      <c r="L56" s="1"/>
+    </row>
+    <row r="57" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J57" s="1"/>
+      <c r="K57"/>
+      <c r="L57" s="1"/>
+    </row>
+    <row r="58" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J58" s="1"/>
+      <c r="K58"/>
+      <c r="L58" s="1"/>
+    </row>
+    <row r="59" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J59" s="1"/>
+      <c r="K59"/>
+      <c r="L59" s="1"/>
+    </row>
+    <row r="60" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J60" s="1"/>
+      <c r="K60"/>
+      <c r="L60" s="1"/>
+    </row>
+    <row r="61" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J61" s="1"/>
+      <c r="K61"/>
+      <c r="L61" s="1"/>
+    </row>
+    <row r="62" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J62" s="1"/>
+      <c r="K62"/>
+      <c r="L62" s="1"/>
+    </row>
+    <row r="63" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J63" s="1"/>
+      <c r="K63"/>
+      <c r="L63" s="1"/>
+    </row>
+    <row r="64" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J64" s="1"/>
+      <c r="K64"/>
+      <c r="L64" s="1"/>
+    </row>
+    <row r="65" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J65" s="1"/>
+      <c r="K65"/>
+      <c r="L65" s="1"/>
+    </row>
+    <row r="66" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J66" s="1"/>
+      <c r="K66"/>
+      <c r="L66" s="1"/>
+    </row>
+    <row r="67" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J67" s="1"/>
+      <c r="K67"/>
+      <c r="L67" s="1"/>
+    </row>
+    <row r="68" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J68" s="1"/>
+      <c r="K68"/>
+      <c r="L68" s="1"/>
+    </row>
+    <row r="69" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J69" s="1"/>
+      <c r="K69"/>
+      <c r="L69" s="1"/>
+    </row>
+    <row r="70" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J70" s="1"/>
+      <c r="K70"/>
+      <c r="L70" s="1"/>
+    </row>
+    <row r="71" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J71" s="1"/>
+      <c r="K71"/>
+      <c r="L71" s="1"/>
+    </row>
+    <row r="72" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J72" s="1"/>
+      <c r="K72"/>
+      <c r="L72" s="1"/>
+    </row>
+    <row r="73" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J73" s="1"/>
+      <c r="K73"/>
+      <c r="L73" s="1"/>
+    </row>
+    <row r="74" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J74" s="1"/>
+      <c r="K74"/>
+      <c r="L74" s="1"/>
+    </row>
+    <row r="75" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J75" s="1"/>
+      <c r="K75"/>
+      <c r="L75" s="1"/>
+    </row>
+    <row r="76" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J76" s="1"/>
+      <c r="K76"/>
+      <c r="L76" s="1"/>
+    </row>
+    <row r="77" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J77" s="1"/>
+      <c r="K77"/>
+      <c r="L77" s="1"/>
+    </row>
+    <row r="78" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J78" s="1"/>
+      <c r="K78"/>
+      <c r="L78" s="1"/>
+    </row>
+    <row r="79" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J79" s="1"/>
+      <c r="K79"/>
+      <c r="L79" s="1"/>
+    </row>
+    <row r="80" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J80" s="1"/>
+      <c r="K80"/>
+      <c r="L80" s="1"/>
+    </row>
+    <row r="81" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J81" s="1"/>
+      <c r="K81"/>
+      <c r="L81" s="1"/>
+    </row>
+    <row r="82" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J82" s="1"/>
+      <c r="K82"/>
+      <c r="L82" s="1"/>
+    </row>
+    <row r="83" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J83" s="1"/>
+      <c r="K83"/>
+      <c r="L83" s="1"/>
+    </row>
+    <row r="84" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J84" s="1"/>
+      <c r="K84"/>
+      <c r="L84" s="1"/>
+    </row>
+    <row r="85" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J85" s="1"/>
+      <c r="K85"/>
+      <c r="L85" s="1"/>
+    </row>
+    <row r="86" ht="16.5" customHeight="1" spans="10:12">
+      <c r="J86" s="1"/>
+      <c r="K86"/>
+      <c r="L86" s="1"/>
+    </row>
     <row r="87" ht="16.5" customHeight="1"/>
     <row r="88" ht="16.5" customHeight="1"/>
     <row r="89" ht="16.5" customHeight="1"/>
@@ -4316,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -4324,17 +4789,10 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:3">
       <c r="A2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" customHeight="1" spans="1:3">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
         <v>29</v>
       </c>
     </row>
+    <row r="3" ht="16.5" customHeight="1"/>
     <row r="4" ht="16.5" customHeight="1"/>
     <row r="5" ht="16.5" customHeight="1"/>
     <row r="6" ht="16.5" customHeight="1"/>
@@ -4797,120 +5255,122 @@
       <c r="E2" t="s">
         <v>147</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="4" t="s">
+        <v>148</v>
+      </c>
       <c r="G2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="T2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="U2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="V2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="W2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="X2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AA2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AB2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AC2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AD2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AH2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AI2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AJ2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AK2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AL2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AM2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AN2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AO2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AP2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AQ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AR2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AS2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AT2">
         <v>14</v>
@@ -4919,58 +5379,58 @@
         <v>100</v>
       </c>
       <c r="AV2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AW2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AX2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AY2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AZ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BA2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BB2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC2">
         <v>9</v>
       </c>
       <c r="BD2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BE2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BF2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BG2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BH2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BI2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BJ2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BL2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BM2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BN2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BO2">
         <v>3000</v>
@@ -4979,7 +5439,7 @@
         <v>5000</v>
       </c>
       <c r="BQ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BR2">
         <v>98</v>
@@ -4988,124 +5448,124 @@
         <v>98</v>
       </c>
       <c r="BT2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BU2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BV2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BW2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BX2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BY2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BZ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CA2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CC2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CE2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CG2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CH2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CI2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CJ2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="CK2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CL2" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="CM2" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="CN2" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="CO2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CP2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="CQ2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="CR2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="CT2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CU2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="CV2" t="s">
+        <v>166</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CX2" t="s">
         <v>165</v>
       </c>
-      <c r="CW2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CX2" t="s">
-        <v>164</v>
-      </c>
       <c r="CZ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="DA2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="DB2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="DC2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="DD2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="DE2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="DF2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="DG2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="DH2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="DI2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="DJ2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="DK2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="DL2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="DN2">
         <v>120</v>
@@ -5150,16 +5610,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:EW28"/>
+  <dimension ref="A1:GA28"/>
   <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="10.6796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.84375" style="1" customWidth="1"/>
     <col min="5" max="5" width="31.1171875" customWidth="1"/>
-    <col min="143" max="143" width="20.8125" customWidth="1"/>
+    <col min="166" max="166" width="20.8125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:153">
+    <row r="1" ht="16.5" customHeight="1" spans="1:183">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -5179,897 +5639,1083 @@
         <v>2</v>
       </c>
       <c r="G1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S1" t="s">
+        <v>53</v>
+      </c>
+      <c r="T1" t="s">
+        <v>54</v>
+      </c>
+      <c r="U1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V1" t="s">
+        <v>56</v>
+      </c>
+      <c r="W1" t="s">
+        <v>57</v>
+      </c>
+      <c r="X1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" t="s">
+      <c r="AE1" t="s">
         <v>37</v>
       </c>
-      <c r="I1" t="s">
+      <c r="AF1" t="s">
         <v>38</v>
       </c>
-      <c r="J1" t="s">
+      <c r="AG1" t="s">
         <v>39</v>
       </c>
-      <c r="K1" t="s">
+      <c r="AH1" t="s">
         <v>40</v>
       </c>
-      <c r="L1" t="s">
+      <c r="AI1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" t="s">
+      <c r="AJ1" t="s">
         <v>42</v>
       </c>
-      <c r="N1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="AK1" t="s">
         <v>172</v>
       </c>
-      <c r="P1" t="s">
+      <c r="AL1" t="s">
         <v>173</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="AM1" t="s">
         <v>174</v>
       </c>
-      <c r="R1" t="s">
+      <c r="AN1" t="s">
         <v>175</v>
       </c>
-      <c r="S1" t="s">
+      <c r="AO1" t="s">
         <v>176</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AP1" t="s">
         <v>177</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AQ1" t="s">
         <v>178</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AR1" t="s">
         <v>179</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AS1" t="s">
         <v>180</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AT1" t="s">
         <v>181</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AU1" t="s">
         <v>182</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AV1" t="s">
         <v>183</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AW1" t="s">
         <v>184</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AX1" t="s">
         <v>185</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AY1" t="s">
         <v>186</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AZ1" t="s">
         <v>187</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="BA1" t="s">
         <v>188</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="BB1" t="s">
         <v>189</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="BC1" t="s">
         <v>190</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="BD1" t="s">
+        <v>191</v>
+      </c>
+      <c r="BE1" t="s">
         <v>83</v>
       </c>
-      <c r="AI1" t="s">
-        <v>191</v>
-      </c>
-      <c r="AK1" t="s">
+      <c r="BF1" t="s">
         <v>192</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="BH1" t="s">
+        <v>193</v>
+      </c>
+      <c r="BI1" t="s">
         <v>73</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="BJ1" t="s">
         <v>74</v>
       </c>
-      <c r="AN1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AO1" t="s">
+      <c r="BK1" t="s">
         <v>194</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="BL1" t="s">
         <v>195</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="BM1" t="s">
+        <v>196</v>
+      </c>
+      <c r="BN1" t="s">
         <v>142</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="BO1" t="s">
         <v>143</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="BP1" t="s">
         <v>38</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="BQ1" t="s">
         <v>144</v>
       </c>
-      <c r="AU1" t="s">
-        <v>196</v>
-      </c>
-      <c r="AV1" t="s">
+      <c r="BR1" t="s">
         <v>197</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BS1" t="s">
         <v>198</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BT1" t="s">
         <v>199</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BU1" t="s">
         <v>200</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BV1" t="s">
         <v>201</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BW1" t="s">
         <v>202</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BX1" t="s">
         <v>203</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BY1" t="s">
         <v>204</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BZ1" t="s">
         <v>205</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="CA1" t="s">
         <v>206</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="CB1" t="s">
         <v>207</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="CC1" t="s">
+        <v>208</v>
+      </c>
+      <c r="CD1" t="s">
         <v>83</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="CE1" t="s">
         <v>84</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="CF1" t="s">
         <v>85</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="CG1" t="s">
         <v>86</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="CH1" t="s">
         <v>87</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="CI1" t="s">
         <v>88</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="CJ1" t="s">
         <v>89</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="CK1" t="s">
         <v>90</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="CL1" t="s">
         <v>120</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="CM1" t="s">
         <v>121</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="CN1" t="s">
         <v>122</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="CO1" t="s">
         <v>123</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="CP1" t="s">
         <v>124</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="CQ1" t="s">
         <v>125</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="CR1" t="s">
         <v>126</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="CS1" t="s">
         <v>127</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="CT1" t="s">
         <v>128</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="CU1" t="s">
         <v>129</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="CV1" t="s">
         <v>130</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CW1" t="s">
         <v>131</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CX1" t="s">
         <v>132</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CY1" t="s">
         <v>140</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CZ1" t="s">
         <v>141</v>
       </c>
-      <c r="CD1" t="s">
-        <v>208</v>
-      </c>
-      <c r="CE1" t="s">
+      <c r="DA1" t="s">
         <v>209</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="DB1" t="s">
         <v>210</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="DC1" t="s">
         <v>211</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="DD1" t="s">
         <v>212</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="DE1" t="s">
+        <v>213</v>
+      </c>
+      <c r="DF1" t="s">
         <v>84</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="DG1" t="s">
         <v>85</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="DH1" t="s">
         <v>86</v>
       </c>
-      <c r="CL1" t="s">
-        <v>213</v>
-      </c>
-      <c r="CM1" t="s">
+      <c r="DI1" t="s">
+        <v>214</v>
+      </c>
+      <c r="DJ1" t="s">
         <v>88</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="DK1" t="s">
         <v>89</v>
       </c>
-      <c r="CO1" t="s">
-        <v>214</v>
-      </c>
-      <c r="CP1" t="s">
+      <c r="DL1" t="s">
         <v>215</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="DM1" t="s">
         <v>216</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="DN1" t="s">
         <v>217</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="DO1" t="s">
         <v>218</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="DP1" t="s">
         <v>219</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="DQ1" t="s">
         <v>220</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="DR1" t="s">
         <v>221</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="DS1" t="s">
         <v>222</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="DT1" t="s">
         <v>223</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DU1" t="s">
         <v>224</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DV1" t="s">
         <v>225</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DW1" t="s">
         <v>226</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DX1" t="s">
         <v>227</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DY1" t="s">
         <v>228</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DZ1" t="s">
         <v>229</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="EA1" t="s">
         <v>230</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="EB1" t="s">
         <v>231</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="EC1" t="s">
         <v>232</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="ED1" t="s">
         <v>233</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="EE1" t="s">
         <v>234</v>
       </c>
-      <c r="DJ1" t="s">
+      <c r="EF1" t="s">
         <v>235</v>
       </c>
-      <c r="DK1" t="s">
+      <c r="EG1" t="s">
         <v>236</v>
       </c>
-      <c r="DL1" t="s">
+      <c r="EH1" t="s">
         <v>237</v>
       </c>
-      <c r="DM1" t="s">
+      <c r="EI1" t="s">
         <v>238</v>
       </c>
-      <c r="DN1" t="s">
+      <c r="EJ1" t="s">
         <v>239</v>
       </c>
-      <c r="DO1" t="s">
+      <c r="EK1" t="s">
         <v>240</v>
       </c>
-      <c r="DP1" t="s">
+      <c r="EL1" t="s">
         <v>241</v>
       </c>
-      <c r="DQ1" t="s">
+      <c r="EM1" t="s">
         <v>242</v>
       </c>
-      <c r="DR1" t="s">
+      <c r="EN1" t="s">
         <v>243</v>
       </c>
-      <c r="DS1" t="s">
+      <c r="EO1" t="s">
         <v>244</v>
       </c>
-      <c r="DT1" t="s">
+      <c r="EP1" t="s">
         <v>245</v>
       </c>
-      <c r="DU1" t="s">
+      <c r="EQ1" t="s">
         <v>246</v>
       </c>
-      <c r="DV1" t="s">
+      <c r="ER1" t="s">
         <v>247</v>
       </c>
-      <c r="DW1" t="s">
+      <c r="ES1" t="s">
         <v>248</v>
       </c>
-      <c r="DX1" t="s">
+      <c r="ET1" t="s">
         <v>249</v>
       </c>
-      <c r="DY1" t="s">
+      <c r="EU1" t="s">
         <v>250</v>
       </c>
-      <c r="DZ1" t="s">
+      <c r="EV1" t="s">
         <v>251</v>
       </c>
-      <c r="EA1" t="s">
+      <c r="EW1" t="s">
         <v>252</v>
       </c>
-      <c r="EB1" t="s">
+      <c r="EX1" t="s">
+        <v>253</v>
+      </c>
+      <c r="EY1" t="s">
         <v>72</v>
       </c>
-      <c r="EC1" t="s">
+      <c r="EZ1" t="s">
         <v>73</v>
       </c>
-      <c r="ED1" t="s">
+      <c r="FA1" t="s">
         <v>74</v>
       </c>
-      <c r="EE1" t="s">
+      <c r="FB1" t="s">
         <v>75</v>
       </c>
-      <c r="EF1" t="s">
+      <c r="FC1" t="s">
         <v>76</v>
       </c>
-      <c r="EG1" t="s">
-        <v>253</v>
-      </c>
-      <c r="EH1" t="s">
+      <c r="FD1" t="s">
         <v>254</v>
       </c>
-      <c r="EI1" t="s">
+      <c r="FE1" t="s">
         <v>255</v>
       </c>
-      <c r="EJ1" t="s">
+      <c r="FF1" t="s">
+        <v>256</v>
+      </c>
+      <c r="FG1" t="s">
         <v>121</v>
       </c>
-      <c r="EK1" t="s">
+      <c r="FH1" t="s">
         <v>122</v>
       </c>
-      <c r="EL1" t="s">
+      <c r="FI1" t="s">
         <v>123</v>
       </c>
-      <c r="EM1" t="s">
+      <c r="FJ1" t="s">
         <v>124</v>
       </c>
-      <c r="EN1" t="s">
-        <v>256</v>
-      </c>
-      <c r="EO1" t="s">
+      <c r="FK1" t="s">
         <v>257</v>
       </c>
-      <c r="EP1" t="s">
+      <c r="FL1" t="s">
+        <v>258</v>
+      </c>
+      <c r="FM1" t="s">
         <v>38</v>
       </c>
-      <c r="EQ1" t="s">
+      <c r="FN1" t="s">
         <v>144</v>
       </c>
-      <c r="ER1" t="s">
-        <v>258</v>
-      </c>
-      <c r="ES1" t="s">
+      <c r="FO1" t="s">
         <v>259</v>
       </c>
-      <c r="ET1" t="s">
+      <c r="FP1" t="s">
         <v>260</v>
       </c>
-      <c r="EU1" t="s">
+      <c r="FQ1" t="s">
         <v>261</v>
       </c>
-      <c r="EV1" t="s">
+      <c r="FR1" t="s">
         <v>262</v>
       </c>
-      <c r="EW1" t="s">
+      <c r="FS1" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" spans="1:153">
+      <c r="FT1" t="s">
+        <v>264</v>
+      </c>
+      <c r="FU1" t="s">
+        <v>65</v>
+      </c>
+      <c r="FV1" t="s">
+        <v>66</v>
+      </c>
+      <c r="FW1" t="s">
+        <v>67</v>
+      </c>
+      <c r="FX1" t="s">
+        <v>68</v>
+      </c>
+      <c r="FY1" t="s">
+        <v>69</v>
+      </c>
+      <c r="FZ1" t="s">
+        <v>70</v>
+      </c>
+      <c r="GA1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" spans="1:183">
       <c r="A2" s="1" t="s">
-        <v>145</v>
+        <v>265</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>146</v>
+        <v>266</v>
       </c>
       <c r="E2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F2" t="s">
-        <v>265</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="F2"/>
       <c r="G2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H2" t="s">
         <v>150</v>
       </c>
+      <c r="I2" t="s">
+        <v>149</v>
+      </c>
       <c r="J2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="R2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="S2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="T2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="U2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="V2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="W2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="X2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Y2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Z2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AA2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AB2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AC2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AD2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AE2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AH2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AI2" t="s">
-        <v>157</v>
+        <v>151</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>151</v>
       </c>
       <c r="AK2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL2">
+        <v>149</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BI2">
         <v>50</v>
       </c>
-      <c r="AM2">
+      <c r="BJ2">
         <v>130</v>
       </c>
-      <c r="AN2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AO2">
+      <c r="BK2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BL2">
         <v>120</v>
       </c>
-      <c r="AP2">
+      <c r="BM2">
         <v>80</v>
       </c>
-      <c r="AQ2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AT2">
+      <c r="BN2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>151</v>
+      </c>
+      <c r="BQ2">
         <v>120</v>
       </c>
-      <c r="AU2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AV2" t="s">
+      <c r="BR2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>167</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>167</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>168</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>153</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>268</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>268</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>151</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>153</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>269</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>270</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>271</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>272</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>273</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>274</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>275</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>276</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CX2" t="s">
+        <v>165</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>162</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>277</v>
+      </c>
+      <c r="DC2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DD2" t="s">
+        <v>278</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DG2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DI2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DK2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DL2" t="s">
+        <v>158</v>
+      </c>
+      <c r="DM2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DN2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DO2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DP2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DQ2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DR2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DS2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DT2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DU2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DV2">
+        <v>4</v>
+      </c>
+      <c r="DW2">
+        <v>3</v>
+      </c>
+      <c r="DX2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DY2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DZ2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EA2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EB2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EC2" t="s">
+        <v>149</v>
+      </c>
+      <c r="ED2" t="s">
+        <v>149</v>
+      </c>
+      <c r="EE2" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="EF2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EG2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EH2" t="s">
+        <v>149</v>
+      </c>
+      <c r="EI2" t="s">
         <v>152</v>
       </c>
-      <c r="AW2" t="s">
-        <v>152</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>166</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>166</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>266</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>266</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>267</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>268</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>269</v>
-      </c>
-      <c r="BS2" t="s">
+      <c r="EJ2" t="s">
+        <v>149</v>
+      </c>
+      <c r="EK2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EL2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EM2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EN2" t="s">
+        <v>149</v>
+      </c>
+      <c r="EO2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EP2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EQ2" t="s">
+        <v>151</v>
+      </c>
+      <c r="ER2" t="s">
+        <v>151</v>
+      </c>
+      <c r="ES2" t="s">
+        <v>149</v>
+      </c>
+      <c r="ET2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EU2" t="s">
+        <v>280</v>
+      </c>
+      <c r="EV2" t="s">
+        <v>281</v>
+      </c>
+      <c r="EW2">
+        <v>1</v>
+      </c>
+      <c r="EX2" t="s">
+        <v>149</v>
+      </c>
+      <c r="EY2" t="s">
+        <v>149</v>
+      </c>
+      <c r="EZ2">
+        <v>40</v>
+      </c>
+      <c r="FA2">
+        <v>130</v>
+      </c>
+      <c r="FB2" t="s">
+        <v>156</v>
+      </c>
+      <c r="FC2" t="s">
+        <v>153</v>
+      </c>
+      <c r="FD2" t="s">
+        <v>149</v>
+      </c>
+      <c r="FE2">
+        <v>30</v>
+      </c>
+      <c r="FF2" t="s">
+        <v>149</v>
+      </c>
+      <c r="FG2" t="s">
+        <v>162</v>
+      </c>
+      <c r="FH2" t="s">
         <v>270</v>
       </c>
-      <c r="BT2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>271</v>
-      </c>
-      <c r="BV2" t="s">
+      <c r="FI2" t="s">
+        <v>164</v>
+      </c>
+      <c r="FJ2" t="s">
         <v>272</v>
       </c>
-      <c r="BW2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BX2" t="s">
-        <v>273</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>274</v>
-      </c>
-      <c r="BZ2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CA2" t="s">
-        <v>164</v>
-      </c>
-      <c r="CB2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CC2" t="s">
-        <v>161</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>275</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>276</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CI2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CJ2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CK2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CL2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CM2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CN2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CO2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CR2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CS2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CT2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CU2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CV2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CW2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CX2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CY2">
-        <v>4</v>
-      </c>
-      <c r="CZ2">
-        <v>3</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DB2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DC2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DD2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DE2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DH2" s="3" t="s">
+      <c r="FK2" t="s">
+        <v>149</v>
+      </c>
+      <c r="FL2" t="s">
+        <v>151</v>
+      </c>
+      <c r="FM2">
+        <v>10</v>
+      </c>
+      <c r="FN2">
+        <v>75</v>
+      </c>
+      <c r="FO2">
+        <v>90</v>
+      </c>
+      <c r="FP2" t="s">
+        <v>149</v>
+      </c>
+      <c r="FQ2" t="s">
+        <v>282</v>
+      </c>
+      <c r="FR2" t="s">
+        <v>149</v>
+      </c>
+      <c r="FS2" t="s">
         <v>277</v>
       </c>
-      <c r="DI2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DJ2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DK2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DL2" t="s">
-        <v>151</v>
-      </c>
-      <c r="DM2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DN2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DO2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DP2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DQ2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DR2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DS2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DT2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DU2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DV2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DW2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DX2" t="s">
-        <v>278</v>
-      </c>
-      <c r="DY2" t="s">
-        <v>279</v>
-      </c>
-      <c r="DZ2">
-        <v>1</v>
-      </c>
-      <c r="EA2" t="s">
-        <v>148</v>
-      </c>
-      <c r="EB2" t="s">
-        <v>148</v>
-      </c>
-      <c r="EC2">
-        <v>40</v>
-      </c>
-      <c r="ED2">
-        <v>130</v>
-      </c>
-      <c r="EE2" t="s">
+      <c r="FT2" t="s">
+        <v>283</v>
+      </c>
+      <c r="FU2" t="s">
+        <v>149</v>
+      </c>
+      <c r="FV2" t="s">
+        <v>153</v>
+      </c>
+      <c r="FW2" t="s">
+        <v>151</v>
+      </c>
+      <c r="FX2" t="s">
+        <v>149</v>
+      </c>
+      <c r="FY2" t="s">
+        <v>154</v>
+      </c>
+      <c r="FZ2" t="s">
+        <v>149</v>
+      </c>
+      <c r="GA2" t="s">
         <v>155</v>
       </c>
-      <c r="EF2" t="s">
-        <v>152</v>
-      </c>
-      <c r="EG2" t="s">
-        <v>148</v>
-      </c>
-      <c r="EH2">
-        <v>30</v>
-      </c>
-      <c r="EI2" t="s">
-        <v>148</v>
-      </c>
-      <c r="EJ2" t="s">
-        <v>161</v>
-      </c>
-      <c r="EK2" t="s">
-        <v>268</v>
-      </c>
-      <c r="EL2" t="s">
-        <v>163</v>
-      </c>
-      <c r="EM2" t="s">
-        <v>270</v>
-      </c>
-      <c r="EN2" t="s">
-        <v>148</v>
-      </c>
-      <c r="EO2" t="s">
-        <v>150</v>
-      </c>
-      <c r="EP2">
-        <v>10</v>
-      </c>
-      <c r="EQ2">
-        <v>75</v>
-      </c>
-      <c r="ER2">
-        <v>90</v>
-      </c>
-      <c r="ES2" t="s">
-        <v>148</v>
-      </c>
-      <c r="ET2" t="s">
-        <v>280</v>
-      </c>
-      <c r="EU2" t="s">
-        <v>148</v>
-      </c>
-      <c r="EV2" t="s">
-        <v>275</v>
-      </c>
-      <c r="EW2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="3" ht="17.25" customHeight="1" spans="1:153">
-      <c r="DH3" s="3"/>
-    </row>
-    <row r="4" ht="17.25" customHeight="1"/>
-    <row r="5" ht="17.25" customHeight="1"/>
-    <row r="6" ht="17.25" customHeight="1"/>
-    <row r="7" ht="17.25" customHeight="1"/>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" spans="1:183">
+      <c r="EE3" s="3"/>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" spans="1:183">
+      <c r="EE4" s="3"/>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" spans="1:183">
+      <c r="EE5" s="3"/>
+    </row>
+    <row r="6" ht="17.25" customHeight="1" spans="1:183">
+      <c r="EE6" s="3"/>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" spans="1:183">
+      <c r="EE7" s="3"/>
+    </row>
     <row r="8" ht="17.25" customHeight="1"/>
     <row r="9" ht="17.25" customHeight="1"/>
     <row r="10" ht="17.25" customHeight="1"/>
@@ -6140,205 +6786,205 @@
         <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K1" t="s">
         <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="R1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="S1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="T1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="U1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="V1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="W1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="X1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Y1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Z1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AB1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AC1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AD1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AE1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AF1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AH1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AI1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AJ1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AK1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AL1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AM1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AN1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AO1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AP1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AQ1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AR1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AS1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AT1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AU1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AV1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AW1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AX1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AY1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AZ1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="BA1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="BB1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="BC1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="BD1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="BE1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="BF1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="BG1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="BH1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="BI1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="BJ1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="BK1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="BL1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="BM1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="BN1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="BO1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="BP1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="BQ1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="BR1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="BS1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="BT1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="BU1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="BV1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BW1" t="s">
         <v>73</v>
@@ -6347,52 +6993,52 @@
         <v>74</v>
       </c>
       <c r="BY1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="BZ1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="CA1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="CB1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="CC1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="CD1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="CE1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="CF1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="CG1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="CH1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="CI1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="CJ1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="CK1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="CL1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="CM1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="CN1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="CO1" t="s">
         <v>84</v>
@@ -6404,7 +7050,7 @@
         <v>86</v>
       </c>
       <c r="CR1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="CS1" t="s">
         <v>88</v>
@@ -6416,7 +7062,7 @@
         <v>90</v>
       </c>
       <c r="CV1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="CW1" t="s">
         <v>121</v>
@@ -6455,7 +7101,7 @@
         <v>132</v>
       </c>
       <c r="DI1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="DJ1" t="s">
         <v>134</v>
@@ -6464,384 +7110,384 @@
         <v>135</v>
       </c>
       <c r="DL1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="DM1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="DN1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="DO1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="DP1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="DQ1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="DR1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="DS1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="DT1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="DU1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="DV1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="DW1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="DX1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="DY1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="DZ1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="EA1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="EB1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="EC1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="ED1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="EE1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="EF1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="EG1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="EH1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="EI1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="EJ1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="EK1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="EL1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="EM1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="EN1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="EO1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="EP1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="EQ1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="ER1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="ES1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="ET1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="EU1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="EV1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="EW1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="EX1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="EY1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="EZ1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="FA1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="FB1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="FC1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="FD1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="FE1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="FF1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="FG1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="FH1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="FI1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="FJ1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="FK1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="FL1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="FM1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="FN1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="FO1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="FP1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="FQ1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="FR1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="FS1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="FT1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="FU1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="FV1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="FW1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="FX1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="FY1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="FZ1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="GA1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="GB1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="GC1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="GD1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="GE1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="GF1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="GG1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="GH1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="GI1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="GJ1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="GK1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="GL1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="GM1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="GN1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="GO1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="GP1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="GQ1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:199">
       <c r="A2" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J2" t="s">
+        <v>151</v>
+      </c>
+      <c r="K2" t="s">
         <v>150</v>
       </c>
-      <c r="J2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K2" t="s">
-        <v>149</v>
-      </c>
       <c r="L2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="S2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="T2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="U2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="V2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="W2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Z2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AB2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AC2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AE2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AF2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AH2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AI2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AJ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AK2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AN2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AO2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AP2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AQ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AR2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AS2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AT2">
         <v>3</v>
@@ -6850,25 +7496,25 @@
         <v>15</v>
       </c>
       <c r="AV2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AW2">
         <v>3</v>
       </c>
       <c r="AX2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AY2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AZ2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="BA2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BB2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC2">
         <v>5</v>
@@ -6877,7 +7523,7 @@
         <v>60</v>
       </c>
       <c r="BE2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BF2">
         <v>6</v>
@@ -6886,7 +7532,7 @@
         <v>30</v>
       </c>
       <c r="BH2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BI2">
         <v>3</v>
@@ -6895,7 +7541,7 @@
         <v>120</v>
       </c>
       <c r="BK2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BL2">
         <v>2</v>
@@ -6904,7 +7550,7 @@
         <v>100</v>
       </c>
       <c r="BN2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BO2">
         <v>1</v>
@@ -6913,7 +7559,7 @@
         <v>20</v>
       </c>
       <c r="BQ2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BR2">
         <v>1</v>
@@ -6922,388 +7568,388 @@
         <v>20</v>
       </c>
       <c r="BT2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BU2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="BV2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BW2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="BX2">
         <v>160</v>
       </c>
       <c r="BY2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="BZ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CA2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CB2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="CC2" t="s">
+        <v>447</v>
+      </c>
+      <c r="CD2" t="s">
         <v>445</v>
       </c>
-      <c r="CD2" t="s">
-        <v>443</v>
-      </c>
       <c r="CE2" t="s">
+        <v>448</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>447</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>151</v>
+      </c>
+      <c r="CI2" t="s">
         <v>446</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CJ2" t="s">
+        <v>449</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>450</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>449</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>450</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>158</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>151</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>151</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>151</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>151</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>151</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>153</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>162</v>
+      </c>
+      <c r="CX2" t="s">
+        <v>270</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>164</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>272</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>165</v>
+      </c>
+      <c r="DC2" t="s">
+        <v>166</v>
+      </c>
+      <c r="DD2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>275</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>451</v>
+      </c>
+      <c r="DG2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>165</v>
+      </c>
+      <c r="DI2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>167</v>
+      </c>
+      <c r="DK2" t="s">
+        <v>168</v>
+      </c>
+      <c r="DL2" t="s">
+        <v>153</v>
+      </c>
+      <c r="DM2" t="s">
+        <v>153</v>
+      </c>
+      <c r="DN2" t="s">
+        <v>452</v>
+      </c>
+      <c r="DO2" t="s">
+        <v>452</v>
+      </c>
+      <c r="DP2" t="s">
+        <v>453</v>
+      </c>
+      <c r="DQ2" t="s">
+        <v>454</v>
+      </c>
+      <c r="DR2" t="s">
+        <v>153</v>
+      </c>
+      <c r="DS2" t="s">
+        <v>153</v>
+      </c>
+      <c r="DT2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DU2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DV2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DW2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DX2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DY2" t="s">
+        <v>151</v>
+      </c>
+      <c r="DZ2" t="s">
+        <v>149</v>
+      </c>
+      <c r="EA2" t="s">
+        <v>455</v>
+      </c>
+      <c r="EB2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EC2" t="s">
+        <v>456</v>
+      </c>
+      <c r="ED2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EE2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EF2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EG2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EH2" t="s">
+        <v>149</v>
+      </c>
+      <c r="EI2" t="s">
         <v>445</v>
       </c>
-      <c r="CG2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CI2" t="s">
-        <v>444</v>
-      </c>
-      <c r="CJ2" t="s">
-        <v>447</v>
-      </c>
-      <c r="CK2" t="s">
-        <v>448</v>
-      </c>
-      <c r="CL2" t="s">
-        <v>447</v>
-      </c>
-      <c r="CM2" t="s">
-        <v>448</v>
-      </c>
-      <c r="CN2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CO2" t="s">
-        <v>157</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CR2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CS2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CT2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CU2" t="s">
-        <v>152</v>
-      </c>
-      <c r="CV2" t="s">
-        <v>148</v>
-      </c>
-      <c r="CW2" t="s">
-        <v>161</v>
-      </c>
-      <c r="CX2" t="s">
-        <v>268</v>
-      </c>
-      <c r="CY2" t="s">
-        <v>163</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>270</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DB2" t="s">
-        <v>164</v>
-      </c>
-      <c r="DC2" t="s">
-        <v>165</v>
-      </c>
-      <c r="DD2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DE2" t="s">
-        <v>273</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>449</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>164</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DJ2" t="s">
-        <v>166</v>
-      </c>
-      <c r="DK2" t="s">
-        <v>167</v>
-      </c>
-      <c r="DL2" t="s">
-        <v>152</v>
-      </c>
-      <c r="DM2" t="s">
-        <v>152</v>
-      </c>
-      <c r="DN2" t="s">
-        <v>450</v>
-      </c>
-      <c r="DO2" t="s">
-        <v>450</v>
-      </c>
-      <c r="DP2" t="s">
-        <v>451</v>
-      </c>
-      <c r="DQ2" t="s">
-        <v>452</v>
-      </c>
-      <c r="DR2" t="s">
-        <v>152</v>
-      </c>
-      <c r="DS2" t="s">
-        <v>152</v>
-      </c>
-      <c r="DT2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DU2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DV2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DW2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DX2" t="s">
-        <v>148</v>
-      </c>
-      <c r="DY2" t="s">
-        <v>150</v>
-      </c>
-      <c r="DZ2" t="s">
-        <v>148</v>
-      </c>
-      <c r="EA2" t="s">
-        <v>453</v>
-      </c>
-      <c r="EB2" t="s">
-        <v>150</v>
-      </c>
-      <c r="EC2" t="s">
-        <v>454</v>
-      </c>
-      <c r="ED2" t="s">
-        <v>150</v>
-      </c>
-      <c r="EE2" t="s">
-        <v>150</v>
-      </c>
-      <c r="EF2" t="s">
-        <v>150</v>
-      </c>
-      <c r="EG2" t="s">
-        <v>150</v>
-      </c>
-      <c r="EH2" t="s">
-        <v>148</v>
-      </c>
-      <c r="EI2" t="s">
-        <v>443</v>
-      </c>
       <c r="EJ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="EK2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="EL2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="EM2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="EN2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="EO2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="EP2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="EQ2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="ER2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="ES2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="ET2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="EU2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="EV2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="EW2">
         <v>0.9</v>
       </c>
       <c r="EX2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="EY2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="EZ2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="FA2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FB2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="FC2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="FD2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FE2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="FF2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="FG2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="FH2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FI2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="FJ2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="FK2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="FL2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="FM2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="FN2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FO2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="FP2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="FQ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FR2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="FS2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="FT2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FU2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="FV2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="FW2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="FX2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FY2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="FZ2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="GA2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="GB2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="GC2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="GD2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="GE2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="GF2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="GG2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="GH2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="GI2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="GJ2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="GK2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="GL2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="GM2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="GN2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="GO2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="GP2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="GQ2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1"/>
@@ -7377,190 +8023,190 @@
         <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I1" t="s">
         <v>35</v>
       </c>
       <c r="J1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O1" t="s">
+        <v>301</v>
+      </c>
+      <c r="P1" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>213</v>
+      </c>
+      <c r="R1" t="s">
+        <v>215</v>
+      </c>
+      <c r="S1" t="s">
+        <v>292</v>
+      </c>
+      <c r="T1" t="s">
+        <v>293</v>
+      </c>
+      <c r="U1" t="s">
+        <v>294</v>
+      </c>
+      <c r="V1" t="s">
+        <v>295</v>
+      </c>
+      <c r="W1" t="s">
+        <v>296</v>
+      </c>
+      <c r="X1" t="s">
+        <v>297</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>298</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA1" t="s">
         <v>299</v>
       </c>
-      <c r="P1" t="s">
+      <c r="AB1" t="s">
         <v>300</v>
       </c>
-      <c r="Q1" t="s">
-        <v>212</v>
-      </c>
-      <c r="R1" t="s">
-        <v>214</v>
-      </c>
-      <c r="S1" t="s">
-        <v>290</v>
-      </c>
-      <c r="T1" t="s">
-        <v>291</v>
-      </c>
-      <c r="U1" t="s">
-        <v>292</v>
-      </c>
-      <c r="V1" t="s">
-        <v>293</v>
-      </c>
-      <c r="W1" t="s">
-        <v>294</v>
-      </c>
-      <c r="X1" t="s">
-        <v>295</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>296</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>245</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>297</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>298</v>
-      </c>
       <c r="AC1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AD1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AE1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AF1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AH1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AI1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AJ1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AK1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AL1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AM1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AP1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AQ1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AR1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AS1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AT1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AU1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AV1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AW1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AX1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AY1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AZ1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="BA1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="BB1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="BC1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="BD1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="BE1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="BF1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="BG1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="BH1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="BI1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="BJ1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="BK1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="BL1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="BM1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="BN1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="BO1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="BP1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="BQ1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="BR1" t="s">
         <v>73</v>
@@ -7569,220 +8215,220 @@
         <v>74</v>
       </c>
       <c r="BT1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="BU1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="BV1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="BW1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="BX1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="BY1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="BZ1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="CA1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="CB1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="CC1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="CD1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="CE1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="CF1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="CG1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="CH1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="CI1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="CJ1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="CK1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="CL1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="CM1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="CN1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="CO1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="CP1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="CQ1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="CR1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="CS1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="CT1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="CU1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="CV1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="CW1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="CX1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="CY1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="CZ1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="DA1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="DB1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="DC1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="DD1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="DE1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="DF1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="DG1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="DH1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="DI1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="DJ1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="DK1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="DL1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="DM1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="DN1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="DO1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="DP1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="DQ1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="DR1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="DS1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="DT1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="DU1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="DV1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="DW1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="DX1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="DY1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="DZ1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="EA1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="EB1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="EC1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="ED1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="EE1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="EF1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="EG1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="EH1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="EI1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="EJ1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="EK1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="EL1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="EM1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="EN1" t="s">
         <v>84</v>
@@ -7794,7 +8440,7 @@
         <v>86</v>
       </c>
       <c r="EQ1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="ER1" t="s">
         <v>88</v>
@@ -7806,7 +8452,7 @@
         <v>90</v>
       </c>
       <c r="EU1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="EV1" t="s">
         <v>121</v>
@@ -7845,7 +8491,7 @@
         <v>132</v>
       </c>
       <c r="FH1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="FI1" t="s">
         <v>134</v>
@@ -7854,229 +8500,229 @@
         <v>135</v>
       </c>
       <c r="FK1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="FL1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="FM1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="FN1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="FO1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="FP1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="FQ1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="FR1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="FS1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="FT1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="FU1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="FV1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="FW1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="FX1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="FY1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="FZ1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="GA1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="GB1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="GC1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="GD1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="GE1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="GF1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="GG1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="GH1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="GI1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="GJ1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="GK1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="GL1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="GM1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="GN1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="GO1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="GP1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="GQ1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="GR1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="GS1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="GT1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="GU1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="GV1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="GW1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="GX1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="GY1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="GZ1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="HA1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="HB1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="HC1" t="s">
+        <v>410</v>
+      </c>
+      <c r="HD1" t="s">
+        <v>411</v>
+      </c>
+      <c r="HE1" t="s">
+        <v>412</v>
+      </c>
+      <c r="HF1" t="s">
+        <v>413</v>
+      </c>
+      <c r="HG1" t="s">
+        <v>414</v>
+      </c>
+      <c r="HH1" t="s">
+        <v>415</v>
+      </c>
+      <c r="HI1" t="s">
+        <v>416</v>
+      </c>
+      <c r="HJ1" t="s">
+        <v>308</v>
+      </c>
+      <c r="HK1" t="s">
+        <v>417</v>
+      </c>
+      <c r="HL1" t="s">
+        <v>418</v>
+      </c>
+      <c r="HM1" t="s">
+        <v>419</v>
+      </c>
+      <c r="HN1" t="s">
+        <v>420</v>
+      </c>
+      <c r="HO1" t="s">
+        <v>421</v>
+      </c>
+      <c r="HP1" t="s">
+        <v>422</v>
+      </c>
+      <c r="HQ1" t="s">
+        <v>423</v>
+      </c>
+      <c r="HR1" t="s">
+        <v>424</v>
+      </c>
+      <c r="HS1" t="s">
+        <v>425</v>
+      </c>
+      <c r="HT1" t="s">
+        <v>426</v>
+      </c>
+      <c r="HU1" t="s">
+        <v>397</v>
+      </c>
+      <c r="HV1" t="s">
+        <v>398</v>
+      </c>
+      <c r="HW1" t="s">
+        <v>399</v>
+      </c>
+      <c r="HX1" t="s">
+        <v>400</v>
+      </c>
+      <c r="HY1" t="s">
+        <v>401</v>
+      </c>
+      <c r="HZ1" t="s">
+        <v>402</v>
+      </c>
+      <c r="IA1" t="s">
+        <v>403</v>
+      </c>
+      <c r="IB1" t="s">
+        <v>404</v>
+      </c>
+      <c r="IC1" t="s">
+        <v>405</v>
+      </c>
+      <c r="ID1" t="s">
+        <v>406</v>
+      </c>
+      <c r="IE1" t="s">
+        <v>407</v>
+      </c>
+      <c r="IF1" t="s">
         <v>408</v>
       </c>
-      <c r="HD1" t="s">
+      <c r="IG1" t="s">
         <v>409</v>
-      </c>
-      <c r="HE1" t="s">
-        <v>410</v>
-      </c>
-      <c r="HF1" t="s">
-        <v>411</v>
-      </c>
-      <c r="HG1" t="s">
-        <v>412</v>
-      </c>
-      <c r="HH1" t="s">
-        <v>413</v>
-      </c>
-      <c r="HI1" t="s">
-        <v>414</v>
-      </c>
-      <c r="HJ1" t="s">
-        <v>306</v>
-      </c>
-      <c r="HK1" t="s">
-        <v>415</v>
-      </c>
-      <c r="HL1" t="s">
-        <v>416</v>
-      </c>
-      <c r="HM1" t="s">
-        <v>417</v>
-      </c>
-      <c r="HN1" t="s">
-        <v>418</v>
-      </c>
-      <c r="HO1" t="s">
-        <v>419</v>
-      </c>
-      <c r="HP1" t="s">
-        <v>420</v>
-      </c>
-      <c r="HQ1" t="s">
-        <v>421</v>
-      </c>
-      <c r="HR1" t="s">
-        <v>422</v>
-      </c>
-      <c r="HS1" t="s">
-        <v>423</v>
-      </c>
-      <c r="HT1" t="s">
-        <v>424</v>
-      </c>
-      <c r="HU1" t="s">
-        <v>395</v>
-      </c>
-      <c r="HV1" t="s">
-        <v>396</v>
-      </c>
-      <c r="HW1" t="s">
-        <v>397</v>
-      </c>
-      <c r="HX1" t="s">
-        <v>398</v>
-      </c>
-      <c r="HY1" t="s">
-        <v>399</v>
-      </c>
-      <c r="HZ1" t="s">
-        <v>400</v>
-      </c>
-      <c r="IA1" t="s">
-        <v>401</v>
-      </c>
-      <c r="IB1" t="s">
-        <v>402</v>
-      </c>
-      <c r="IC1" t="s">
-        <v>403</v>
-      </c>
-      <c r="ID1" t="s">
-        <v>404</v>
-      </c>
-      <c r="IE1" t="s">
-        <v>405</v>
-      </c>
-      <c r="IF1" t="s">
-        <v>406</v>
-      </c>
-      <c r="IG1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1" spans="1:241">
@@ -8087,130 +8733,130 @@
         <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="S2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="T2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="U2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="V2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="W2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Z2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AB2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AC2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AE2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AF2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AH2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AI2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AJ2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AK2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AM2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AN2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AO2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AP2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AQ2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AT2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AW2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AX2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AY2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AZ2">
         <v>5</v>
@@ -8219,7 +8865,7 @@
         <v>60</v>
       </c>
       <c r="BB2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BC2">
         <v>6</v>
@@ -8228,7 +8874,7 @@
         <v>30</v>
       </c>
       <c r="BE2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BF2">
         <v>3</v>
@@ -8237,7 +8883,7 @@
         <v>120</v>
       </c>
       <c r="BH2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BI2">
         <v>2</v>
@@ -8246,7 +8892,7 @@
         <v>100</v>
       </c>
       <c r="BK2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BL2">
         <v>1</v>
@@ -8255,7 +8901,7 @@
         <v>20</v>
       </c>
       <c r="BN2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BO2">
         <v>1</v>
@@ -8264,28 +8910,28 @@
         <v>20</v>
       </c>
       <c r="BQ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BR2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="BS2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="BT2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="BU2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BV2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BW2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="BX2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="BY2">
         <v>100</v>
@@ -8297,19 +8943,19 @@
         <v>115</v>
       </c>
       <c r="CB2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CC2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CD2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="CE2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="CF2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="CG2">
         <v>110</v>
@@ -8318,355 +8964,355 @@
         <v>80</v>
       </c>
       <c r="CI2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CJ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CK2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="CL2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CM2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CN2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CO2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CP2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CQ2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CR2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CS2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CT2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CU2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="CV2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="CW2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="CX2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="CY2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="CZ2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="DA2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="DB2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="DC2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="DD2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="DE2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="DF2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="DG2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="DH2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="DI2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="DJ2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="DK2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="DL2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="DM2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="DN2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="DO2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="DP2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="DQ2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="DR2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="DS2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="DT2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="DU2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="DV2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="DW2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="DX2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="DY2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="DZ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="EA2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="EB2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="EC2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="ED2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="EE2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="EF2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="EG2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="EH2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="EI2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="EJ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="EK2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="EL2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="EM2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="EN2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="EO2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="EP2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="EQ2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="ER2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="ES2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="ET2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="EU2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="EV2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="EW2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="EX2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="EY2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="EZ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FA2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="FB2" t="s">
+        <v>166</v>
+      </c>
+      <c r="FC2" t="s">
+        <v>149</v>
+      </c>
+      <c r="FD2" t="s">
         <v>165</v>
       </c>
-      <c r="FC2" t="s">
-        <v>148</v>
-      </c>
-      <c r="FD2" t="s">
-        <v>164</v>
-      </c>
       <c r="FE2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="FF2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FG2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="FH2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FI2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="FJ2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="FK2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="FL2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="FM2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="FN2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="FO2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="FP2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="FQ2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="FR2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="FS2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FT2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FU2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="FV2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FW2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="FX2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="FY2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FZ2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="GA2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GB2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="GC2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GD2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GE2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GF2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GG2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="GH2">
         <v>90</v>
       </c>
       <c r="GI2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="GJ2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="GK2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="GL2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="GM2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="GN2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="GO2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="GP2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="GQ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="GR2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="GS2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="GT2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="GU2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="GV2">
         <v>0.5</v>
@@ -8681,106 +9327,106 @@
         <v>10</v>
       </c>
       <c r="GZ2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="HA2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="HB2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="HC2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="HD2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="HE2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="HF2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="HG2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="HH2" t="s">
+        <v>470</v>
+      </c>
+      <c r="HI2" t="s">
+        <v>159</v>
+      </c>
+      <c r="HJ2" t="s">
+        <v>149</v>
+      </c>
+      <c r="HK2" t="s">
+        <v>21</v>
+      </c>
+      <c r="HL2" t="s">
+        <v>471</v>
+      </c>
+      <c r="HM2" t="s">
+        <v>472</v>
+      </c>
+      <c r="HN2" t="s">
+        <v>473</v>
+      </c>
+      <c r="HO2" t="s">
+        <v>474</v>
+      </c>
+      <c r="HP2" t="s">
+        <v>475</v>
+      </c>
+      <c r="HQ2" t="s">
+        <v>476</v>
+      </c>
+      <c r="HR2" t="s">
+        <v>477</v>
+      </c>
+      <c r="HS2" t="s">
+        <v>478</v>
+      </c>
+      <c r="HT2" t="s">
+        <v>153</v>
+      </c>
+      <c r="HU2" t="s">
+        <v>149</v>
+      </c>
+      <c r="HV2" t="s">
+        <v>467</v>
+      </c>
+      <c r="HW2" t="s">
+        <v>153</v>
+      </c>
+      <c r="HX2" t="s">
+        <v>153</v>
+      </c>
+      <c r="HY2" t="s">
+        <v>149</v>
+      </c>
+      <c r="HZ2" t="s">
         <v>468</v>
       </c>
-      <c r="HI2" t="s">
-        <v>158</v>
-      </c>
-      <c r="HJ2" t="s">
-        <v>148</v>
-      </c>
-      <c r="HK2" t="s">
-        <v>18</v>
-      </c>
-      <c r="HL2" t="s">
-        <v>469</v>
-      </c>
-      <c r="HM2" t="s">
-        <v>470</v>
-      </c>
-      <c r="HN2" t="s">
-        <v>471</v>
-      </c>
-      <c r="HO2" t="s">
-        <v>472</v>
-      </c>
-      <c r="HP2" t="s">
-        <v>473</v>
-      </c>
-      <c r="HQ2" t="s">
-        <v>474</v>
-      </c>
-      <c r="HR2" t="s">
-        <v>475</v>
-      </c>
-      <c r="HS2" t="s">
-        <v>476</v>
-      </c>
-      <c r="HT2" t="s">
-        <v>152</v>
-      </c>
-      <c r="HU2" t="s">
-        <v>148</v>
-      </c>
-      <c r="HV2" t="s">
-        <v>465</v>
-      </c>
-      <c r="HW2" t="s">
-        <v>152</v>
-      </c>
-      <c r="HX2" t="s">
-        <v>152</v>
-      </c>
-      <c r="HY2" t="s">
-        <v>148</v>
-      </c>
-      <c r="HZ2" t="s">
-        <v>466</v>
-      </c>
       <c r="IA2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="IB2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="IC2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="ID2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="IE2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="IF2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="IG2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1"/>
@@ -8802,262 +9448,262 @@
     <row r="19" ht="14.25" customHeight="1"/>
     <row r="20" ht="14.25" customHeight="1" spans="181:188">
       <c r="FY20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FZ20" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="GA20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GB20" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="GC20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GD20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GE20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GF20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="181:188">
       <c r="FY21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FZ21" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="GA21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GB21" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="GC21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GD21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GE21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GF21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1" spans="181:188">
       <c r="FY22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FZ22" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="GA22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GB22" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="GC22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GD22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GE22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GF22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="181:188">
       <c r="FY23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FZ23" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="GA23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GB23" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="GC23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GD23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GE23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GF23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" spans="181:188">
       <c r="FY24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FZ24" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="GA24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GB24" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="GC24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GD24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GE24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GF24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1" spans="181:188">
       <c r="FY25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FZ25" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="GA25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GB25" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="GC25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GD25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GE25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GF25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1" spans="181:188">
       <c r="FY26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FZ26" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="GA26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GB26" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="GC26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GD26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GE26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GF26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1" spans="181:188">
       <c r="FY27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FZ27" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="GA27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GB27" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="GC27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GD27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GE27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GF27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1" spans="181:188">
       <c r="FY28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FZ28" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="GA28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GB28" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="GC28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GD28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GE28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GF28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1" spans="181:188">
       <c r="FY29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="FZ29" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="GA29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GB29" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="GC29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GD29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GE29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="GF29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -9120,10 +9766,10 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>14</v>
@@ -9143,64 +9789,64 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:21">
       <c r="A2" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>574</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="3" ht="22.7" customHeight="1" spans="1:21">
@@ -9222,16 +9868,16 @@
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:5">
       <c r="A1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
